--- a/artfynd/A 40590-2025 artfynd.xlsx
+++ b/artfynd/A 40590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129783229</v>
+        <v>129782925</v>
       </c>
       <c r="B2" t="n">
-        <v>58413</v>
+        <v>58106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502383</v>
+        <v>502369</v>
       </c>
       <c r="R2" t="n">
-        <v>6523647</v>
+        <v>6523710</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129782925</v>
+        <v>129783229</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>58413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -812,7 +812,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502369</v>
+        <v>502383</v>
       </c>
       <c r="R3" t="n">
-        <v>6523710</v>
+        <v>6523647</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 40590-2025 artfynd.xlsx
+++ b/artfynd/A 40590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129782925</v>
+        <v>129783229</v>
       </c>
       <c r="B2" t="n">
-        <v>58106</v>
+        <v>58413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502369</v>
+        <v>502383</v>
       </c>
       <c r="R2" t="n">
-        <v>6523710</v>
+        <v>6523647</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129783229</v>
+        <v>129782925</v>
       </c>
       <c r="B3" t="n">
-        <v>58413</v>
+        <v>58106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -812,7 +812,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502383</v>
+        <v>502369</v>
       </c>
       <c r="R3" t="n">
-        <v>6523647</v>
+        <v>6523710</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 40590-2025 artfynd.xlsx
+++ b/artfynd/A 40590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129783229</v>
+        <v>129782925</v>
       </c>
       <c r="B2" t="n">
-        <v>58413</v>
+        <v>58108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502383</v>
+        <v>502369</v>
       </c>
       <c r="R2" t="n">
-        <v>6523647</v>
+        <v>6523710</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129782925</v>
+        <v>129783229</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>58416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -812,7 +812,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502369</v>
+        <v>502383</v>
       </c>
       <c r="R3" t="n">
-        <v>6523710</v>
+        <v>6523647</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
         <v>129783250</v>
       </c>
       <c r="B4" t="n">
-        <v>58413</v>
+        <v>58416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40590-2025 artfynd.xlsx
+++ b/artfynd/A 40590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129782925</v>
+        <v>129783229</v>
       </c>
       <c r="B2" t="n">
-        <v>58108</v>
+        <v>58419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502369</v>
+        <v>502383</v>
       </c>
       <c r="R2" t="n">
-        <v>6523710</v>
+        <v>6523647</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129783229</v>
+        <v>129782925</v>
       </c>
       <c r="B3" t="n">
-        <v>58416</v>
+        <v>58111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -812,7 +812,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502383</v>
+        <v>502369</v>
       </c>
       <c r="R3" t="n">
-        <v>6523647</v>
+        <v>6523710</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
         <v>129783250</v>
       </c>
       <c r="B4" t="n">
-        <v>58416</v>
+        <v>58419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40590-2025 artfynd.xlsx
+++ b/artfynd/A 40590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129783229</v>
+        <v>129782925</v>
       </c>
       <c r="B2" t="n">
-        <v>58419</v>
+        <v>58111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502383</v>
+        <v>502369</v>
       </c>
       <c r="R2" t="n">
-        <v>6523647</v>
+        <v>6523710</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129782925</v>
+        <v>129783229</v>
       </c>
       <c r="B3" t="n">
-        <v>58111</v>
+        <v>58419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -812,7 +812,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502369</v>
+        <v>502383</v>
       </c>
       <c r="R3" t="n">
-        <v>6523710</v>
+        <v>6523647</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 40590-2025 artfynd.xlsx
+++ b/artfynd/A 40590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129782925</v>
+        <v>129783229</v>
       </c>
       <c r="B2" t="n">
-        <v>58111</v>
+        <v>58419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502369</v>
+        <v>502383</v>
       </c>
       <c r="R2" t="n">
-        <v>6523710</v>
+        <v>6523647</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129783229</v>
+        <v>129782925</v>
       </c>
       <c r="B3" t="n">
-        <v>58419</v>
+        <v>58111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -812,7 +812,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502383</v>
+        <v>502369</v>
       </c>
       <c r="R3" t="n">
-        <v>6523647</v>
+        <v>6523710</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 40590-2025 artfynd.xlsx
+++ b/artfynd/A 40590-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129783229</v>
+        <v>129782925</v>
       </c>
       <c r="B2" t="n">
-        <v>58419</v>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502383</v>
+        <v>502369</v>
       </c>
       <c r="R2" t="n">
-        <v>6523647</v>
+        <v>6523710</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129782925</v>
+        <v>129783229</v>
       </c>
       <c r="B3" t="n">
-        <v>58111</v>
+        <v>58420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -812,7 +812,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502369</v>
+        <v>502383</v>
       </c>
       <c r="R3" t="n">
-        <v>6523710</v>
+        <v>6523647</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
         <v>129783250</v>
       </c>
       <c r="B4" t="n">
-        <v>58419</v>
+        <v>58420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
